--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>Breslow</t>
+    <t>MM2</t>
   </si>
   <si>
     <t>Event</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-breslow-tiefe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
